--- a/3_Power Management/Power Management.xlsx
+++ b/3_Power Management/Power Management.xlsx
@@ -4,19 +4,17 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="300" windowWidth="18495" windowHeight="11700"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
-    <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="201">
   <si>
     <t>BOARD</t>
   </si>
@@ -24,44 +22,610 @@
     <t>COMPONENT</t>
   </si>
   <si>
+    <t>N°</t>
+  </si>
+  <si>
+    <t>VOLTAGE PINS</t>
+  </si>
+  <si>
+    <t>RATING (V)</t>
+  </si>
+  <si>
+    <t>SELECTED VOLTAGE (V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOLTAGE RAIL </t>
+  </si>
+  <si>
+    <t>SEQUENCE</t>
+  </si>
+  <si>
+    <t>FPGA</t>
+  </si>
+  <si>
+    <t>VCCO_O</t>
+  </si>
+  <si>
+    <t>VCCBAT, VCCADC, VCCAUX</t>
+  </si>
+  <si>
+    <t>VCCBRAM, VCCINT</t>
+  </si>
+  <si>
+    <t>CURRENT (mA)</t>
+  </si>
+  <si>
+    <t>+3V3_FPGA</t>
+  </si>
+  <si>
+    <t>+1V8_FPGA</t>
+  </si>
+  <si>
+    <t>+1V0_FPGA</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>VCC</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>AVDD</t>
+  </si>
+  <si>
+    <t>DVDD</t>
+  </si>
+  <si>
+    <t>[2,7-5,5]</t>
+  </si>
+  <si>
+    <t>+3V3</t>
+  </si>
+  <si>
+    <t>STM32F746ZGT7</t>
+  </si>
+  <si>
+    <t>XC7A50T-2FTG256</t>
+  </si>
+  <si>
+    <t>AD9708</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>ADF4382</t>
+  </si>
+  <si>
+    <t>V5_VCO</t>
+  </si>
+  <si>
+    <t>V5_CAL</t>
+  </si>
+  <si>
+    <t>V5_CP</t>
+  </si>
+  <si>
+    <t>V3V3_1</t>
+  </si>
+  <si>
+    <t>V3V3_2</t>
+  </si>
+  <si>
+    <t>[4,75-5,25]</t>
+  </si>
+  <si>
+    <t>[3,15-3,45]</t>
+  </si>
+  <si>
+    <t>ENABLE V</t>
+  </si>
+  <si>
+    <t>MICROCONTROLLER</t>
+  </si>
+  <si>
+    <t>CLOCK SYNTHESIZER</t>
+  </si>
+  <si>
+    <t>VDD</t>
+  </si>
+  <si>
+    <t>RF SWITCH</t>
+  </si>
+  <si>
+    <t>M3SWA2-34DR+</t>
+  </si>
+  <si>
+    <t>VEE</t>
+  </si>
+  <si>
+    <t>[3,3-3,6]</t>
+  </si>
+  <si>
+    <t>OPAMP</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>PHASER</t>
+  </si>
+  <si>
+    <t>ADAR1000</t>
+  </si>
+  <si>
+    <t>AVDD1</t>
+  </si>
+  <si>
+    <t>AVDD3</t>
+  </si>
+  <si>
+    <t>[-5--4,75]</t>
+  </si>
+  <si>
+    <t>[3,1-3,5]</t>
+  </si>
+  <si>
+    <t>RF FRONT END</t>
+  </si>
+  <si>
+    <t>ADTR1107</t>
+  </si>
+  <si>
+    <t>VDD_LNA</t>
+  </si>
+  <si>
+    <t>VGG_LNA</t>
+  </si>
+  <si>
+    <t>VSS_SW</t>
+  </si>
+  <si>
+    <t>VDD_SW</t>
+  </si>
+  <si>
+    <t>VGG_PA</t>
+  </si>
+  <si>
+    <t>VDD_PA</t>
+  </si>
+  <si>
+    <t>ADAR1000 CON</t>
+  </si>
+  <si>
+    <t>[-3,6-0,3]</t>
+  </si>
+  <si>
+    <t>[-0,3-3,6]</t>
+  </si>
+  <si>
+    <t>[3.3-5,5]</t>
+  </si>
+  <si>
+    <t>1. Connect all GND pins to ground.</t>
+  </si>
+  <si>
+    <t>2. Set the VDD_SW pin to 3.3 V.</t>
+  </si>
+  <si>
+    <t>3. Set the VSS_SW pin to −3.3 V.</t>
+  </si>
+  <si>
+    <t>4. Set the CTRL_SW pin to 0 V.</t>
+  </si>
+  <si>
+    <t>5. Set the VGG_LNA pin to 0 V.</t>
+  </si>
+  <si>
+    <t>6. Set the VDD_LNA pin to 0 V.</t>
+  </si>
+  <si>
+    <t>7. Set the VGG_PA pin to −1.75 V.</t>
+  </si>
+  <si>
+    <t>8. Set the VDD_PA pin to 5 V.</t>
+  </si>
+  <si>
+    <t>9. Increase the VGG_PA voltage to achieve the desired IDQ_PA.</t>
+  </si>
+  <si>
+    <t>10. Apply the RF signal to the TX_IN pin.</t>
+  </si>
+  <si>
+    <t>1. Turn off the RF signal.</t>
+  </si>
+  <si>
+    <t>2. Decrease the VGG_PA voltage to −1.75 V.</t>
+  </si>
+  <si>
+    <t>3. Set the VDD_PA pin to 0 V.</t>
+  </si>
+  <si>
+    <t>4. Set the VSS_SW pin to 0 V.</t>
+  </si>
+  <si>
+    <t>5. Set the VDD_SW pin to 0 V.</t>
+  </si>
+  <si>
+    <t>TX Power_down</t>
+  </si>
+  <si>
+    <t>RX Power-up</t>
+  </si>
+  <si>
+    <t>4. Set the CTRL_SW pin to 3.3 V.</t>
+  </si>
+  <si>
+    <t>5. Set the VGG_PA pin to −1.75 V.</t>
+  </si>
+  <si>
+    <t>6. Set the VDD_PA pin to 0 V.</t>
+  </si>
+  <si>
+    <t>7. Set the VGG_LNA pin to 0 V.</t>
+  </si>
+  <si>
+    <t>8. Set the VDD_LNA pin to 3.3 V.</t>
+  </si>
+  <si>
+    <t>9. Apply the RF signal to the ANT pin.</t>
+  </si>
+  <si>
+    <t>RX Power_down</t>
+  </si>
+  <si>
+    <t>2. Set the VDD_LNA pin to 0 V.</t>
+  </si>
+  <si>
+    <t>3. Set the CTRL_SW pin to 0 V.</t>
+  </si>
+  <si>
+    <t>VCCIO, VPLL, VPHY, VREGIN</t>
+  </si>
+  <si>
+    <t>VREGOUT --&gt;  VCORE</t>
+  </si>
+  <si>
+    <t>+3V4</t>
+  </si>
+  <si>
+    <t>[-3,6--3,3]</t>
+  </si>
+  <si>
+    <t>-3V4</t>
+  </si>
+  <si>
+    <t>+1V8_FT</t>
+  </si>
+  <si>
+    <t>+3V3_ADAR12 | +3V3_ADAR34</t>
+  </si>
+  <si>
+    <t>+3V3_ADTR</t>
+  </si>
+  <si>
+    <t>+3V3_VDD_SW</t>
+  </si>
+  <si>
+    <t>+5V0_PA_1 | +5V0_PA_2 | +5V0_PA_3</t>
+  </si>
+  <si>
+    <t>IMU</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>DAC PA</t>
+  </si>
+  <si>
+    <t>OPAMP PA</t>
+  </si>
+  <si>
+    <t>V+</t>
+  </si>
+  <si>
+    <t>V-</t>
+  </si>
+  <si>
+    <t>[2-6]</t>
+  </si>
+  <si>
+    <t>[-6--2]</t>
+  </si>
+  <si>
+    <t>Vcc</t>
+  </si>
+  <si>
+    <t>[2,7-5]</t>
+  </si>
+  <si>
+    <t>OPA4703NA/250</t>
+  </si>
+  <si>
+    <t>Temperature Sensor</t>
+  </si>
+  <si>
+    <t>ADS7830</t>
+  </si>
+  <si>
+    <t>AD9484</t>
+  </si>
+  <si>
+    <t>DRVDD</t>
+  </si>
+  <si>
+    <t>[1,75-1,9]</t>
+  </si>
+  <si>
+    <t>RF POWER AMPLIFIER</t>
+  </si>
+  <si>
+    <t>VD</t>
+  </si>
+  <si>
+    <t>VG</t>
+  </si>
+  <si>
+    <t>[18-22]</t>
+  </si>
+  <si>
+    <t>Bias-up Procedure</t>
+  </si>
+  <si>
+    <t>Turn off RF signal</t>
+  </si>
+  <si>
+    <t>Set VD to 0 V</t>
+  </si>
+  <si>
+    <t>Turn off VD supply</t>
+  </si>
+  <si>
+    <t>Turn off VG supply</t>
+  </si>
+  <si>
+    <t>Vs</t>
+  </si>
+  <si>
+    <t>DAC5578</t>
+  </si>
+  <si>
+    <t>+5V5_PA</t>
+  </si>
+  <si>
+    <t>-5V5_PA</t>
+  </si>
+  <si>
+    <t>VREF</t>
+  </si>
+  <si>
+    <t>[2,5-5]</t>
+  </si>
+  <si>
+    <t>GY-85</t>
+  </si>
+  <si>
+    <t>VCC0_BANK</t>
+  </si>
+  <si>
+    <t>VCCO_BANK x 3</t>
+  </si>
+  <si>
+    <t>STEPPER MOTOR DRIVER</t>
+  </si>
+  <si>
+    <t>TBS6600</t>
+  </si>
+  <si>
+    <t>[9-42]</t>
+  </si>
+  <si>
+    <t>Bias-Down Procedure</t>
+  </si>
+  <si>
+    <t>Set ID limit to 2840 mA, IG limit to 10 mA</t>
+  </si>
+  <si>
+    <t>Set VG to −4.0 V</t>
+  </si>
+  <si>
+    <t>Set VD +22 V</t>
+  </si>
+  <si>
+    <t>Adjust VG more positive until IDQ = 1680 mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply RF signal </t>
+  </si>
+  <si>
+    <t>Reduce VG to −4.0 V. Ensure IDQ ~ 0 mA</t>
+  </si>
+  <si>
+    <t>QPA2962</t>
+  </si>
+  <si>
+    <t>[-4--1,2]</t>
+  </si>
+  <si>
+    <t>CURRENT SENSOR PA</t>
+  </si>
+  <si>
+    <t>INA241A3</t>
+  </si>
+  <si>
+    <t>[2,7-20]</t>
+  </si>
+  <si>
+    <t>LTC5552</t>
+  </si>
+  <si>
+    <t>[3,0-3,6]</t>
+  </si>
+  <si>
+    <t>AD9523</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> bring the 1.8 V supplies high and stable prior to or simultaneously with the 3.3 V supplies. It
+is recommended to hold the RESET pin low while both supply
+domains settle to ensure that the 3.3 V supplies do not lead the 1.8 V supplies</t>
+  </si>
+  <si>
+    <t>VDD3_REF, VDD3_PLL, VDD3_OUT</t>
+  </si>
+  <si>
+    <t>VDD1.8_OUT</t>
+  </si>
+  <si>
+    <t>+3V3_CLOCK</t>
+  </si>
+  <si>
+    <t>+1V8_CLOCK</t>
+  </si>
+  <si>
+    <t>AD8352</t>
+  </si>
+  <si>
+    <t>[3-5,5]</t>
+  </si>
+  <si>
+    <t>MAIN BOARD</t>
+  </si>
+  <si>
+    <t>CLOCKS &amp; FREQUENCY SYNTHESIZER BOARD</t>
+  </si>
+  <si>
+    <t>MICROWAVE POWER AMPLIFIER BOARD</t>
+  </si>
+  <si>
+    <t>ECOC-2522-100.000-3FC</t>
+  </si>
+  <si>
+    <t>OCXO</t>
+  </si>
+  <si>
+    <t>XO</t>
+  </si>
+  <si>
+    <t>CCHD-957-100</t>
+  </si>
+  <si>
+    <t>CVHD-950-100.000</t>
+  </si>
+  <si>
+    <t>VCXO</t>
+  </si>
+  <si>
+    <t>+3V3_XO</t>
+  </si>
+  <si>
+    <t>[3-3,6]</t>
+  </si>
+  <si>
+    <t>3,3/2</t>
+  </si>
+  <si>
+    <t>[3,135-3,465]</t>
+  </si>
+  <si>
+    <t>NEO-6M</t>
+  </si>
+  <si>
+    <t>COOLING SYSTEM</t>
+  </si>
+  <si>
+    <t>MISCELLANEOUS</t>
+  </si>
+  <si>
+    <t>+22V0</t>
+  </si>
+  <si>
+    <t>TMP37</t>
+  </si>
+  <si>
     <t>PART NUMBER</t>
   </si>
   <si>
-    <t>VOLTAGE PINS</t>
-  </si>
-  <si>
-    <t>RATING (V)</t>
-  </si>
-  <si>
-    <t>CURRENT (mA)</t>
-  </si>
-  <si>
-    <t>SELECTED VOLTAGE (V)</t>
-  </si>
-  <si>
-    <t>ENABLE V</t>
-  </si>
-  <si>
-    <t>SEQUENCE</t>
-  </si>
-  <si>
-    <t>QUANTITY</t>
-  </si>
-  <si>
-    <t>TOTAL CURRENT (mA)</t>
-  </si>
-  <si>
-    <t>VOLTAGE RAIL NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTERED VOLTAGE RAIL NAME </t>
+    <t>Mixer</t>
+  </si>
+  <si>
+    <t>+5V0_LO</t>
+  </si>
+  <si>
+    <t>+3V3_LO_1</t>
+  </si>
+  <si>
+    <t>+3V3_LO_2</t>
+  </si>
+  <si>
+    <t>+3V3_AN</t>
+  </si>
+  <si>
+    <t>+5V0_0</t>
+  </si>
+  <si>
+    <t>Apply when temperature reaches a threshold (Relay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX Power_up </t>
+  </si>
+  <si>
+    <t>It is recommended to power up the AVDD3 pins (3.3 V) before or at the same time as the AVDD1 pin (−5 V)</t>
+  </si>
+  <si>
+    <t>ADC PA &amp; T°C Sensor</t>
+  </si>
+  <si>
+    <t>VOLTAGE RAIL AFTER BRANCHING AND FILTERING</t>
+  </si>
+  <si>
+    <t>+3V3_AN1_F |+3V3_AN2_F</t>
+  </si>
+  <si>
+    <t>+3V3_AN3_F</t>
+  </si>
+  <si>
+    <t>+3V3_AN4_F</t>
+  </si>
+  <si>
+    <t>+3V3_AN5_F | +3V3_AN6_F</t>
+  </si>
+  <si>
+    <t>+1V8_CLOCK_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3V3_ADAR1_F | +3V3_ADAR2_F | +3V3_ADAR3_F | +3V3_ADAR4_F </t>
+  </si>
+  <si>
+    <t>-3V3_SW</t>
+  </si>
+  <si>
+    <t>-5V0_ADAR12 |-5V0_ADAR34</t>
+  </si>
+  <si>
+    <t>Barometer</t>
+  </si>
+  <si>
+    <t>BMP180</t>
+  </si>
+  <si>
+    <t>USB 3</t>
+  </si>
+  <si>
+    <t>FT601</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,6 +636,35 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,7 +685,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -101,15 +694,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -122,10 +718,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -134,7 +730,20 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -143,30 +752,727 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -174,7 +1480,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -463,84 +1777,2020 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:M99"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="27" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.28515625" style="50" customWidth="1"/>
+    <col min="10" max="10" width="36" style="50" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="61.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="79.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
-    <row r="2" spans="1:14" s="6" customFormat="1" ht="69.75" customHeight="1" thickBot="1">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:13" s="73" customFormat="1" ht="33" customHeight="1" thickBot="1">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C1" s="70" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E1" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="71" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="71" t="s">
+        <v>188</v>
+      </c>
+      <c r="K1" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="112" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="113"/>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A2" s="108" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="105" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="105" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="105">
+        <v>1</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="G2" s="21">
+        <v>1200</v>
+      </c>
+      <c r="H2" s="21">
+        <v>3.3</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="J2" s="45"/>
+      <c r="K2" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="22"/>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A3" s="109"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I3" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="J3" s="74"/>
+      <c r="K3" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="23"/>
+    </row>
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A4" s="109"/>
+      <c r="B4" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="5">
+        <v>25</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="I4" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="74"/>
+      <c r="K4" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="23"/>
+    </row>
+    <row r="5" spans="1:13" s="2" customFormat="1">
+      <c r="A5" s="109"/>
+      <c r="B5" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="5">
+        <v>25</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="I5" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="J5" s="74"/>
+      <c r="K5" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="23"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="109"/>
+      <c r="B6" s="100" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="100" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="100">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G6" s="8">
+        <v>250</v>
+      </c>
+      <c r="H6" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J6" s="14"/>
+      <c r="K6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="111" t="s">
+        <v>152</v>
+      </c>
+      <c r="M6" s="24"/>
+    </row>
+    <row r="7" spans="1:13" ht="60" customHeight="1">
+      <c r="A7" s="109"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="G7" s="8">
+        <v>250</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="111"/>
+      <c r="M7" s="24"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="109"/>
+      <c r="B8" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="100">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="8">
+        <v>200</v>
+      </c>
+      <c r="H8" s="8">
+        <v>5</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="109"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="H9" s="8">
+        <v>5</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="14"/>
+      <c r="K9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="24"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="109"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="8">
+        <v>70</v>
+      </c>
+      <c r="H10" s="8">
+        <v>5</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="14"/>
+      <c r="K10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="109"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="8">
+        <v>240</v>
+      </c>
+      <c r="H11" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J11" s="14"/>
+      <c r="K11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" thickBot="1">
+      <c r="A12" s="110"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="26">
+        <v>340</v>
+      </c>
+      <c r="H12" s="26">
+        <v>3.3</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="J12" s="47"/>
+      <c r="K12" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="27"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1">
+      <c r="A13" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="28">
+        <v>1</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="28">
+        <v>3.3</v>
+      </c>
+      <c r="G13" s="28">
+        <v>130</v>
+      </c>
+      <c r="H13" s="28">
+        <v>3.3</v>
+      </c>
+      <c r="I13" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="48"/>
+      <c r="K13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="30"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="87"/>
+      <c r="B14" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="100">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="G14" s="8">
+        <v>50</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="14"/>
+      <c r="K14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="8"/>
+      <c r="M14" s="24"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="87"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F15" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G15" s="8">
+        <v>20</v>
+      </c>
+      <c r="H15" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="14"/>
+      <c r="K15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="87"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="G16" s="8">
+        <v>22</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="14"/>
+      <c r="K16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="87"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8">
+        <v>30</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="14"/>
+      <c r="K17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="87"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G18" s="8">
+        <v>200</v>
+      </c>
+      <c r="H18" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="14"/>
+      <c r="K18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="8"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="87"/>
+      <c r="B19" s="101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="100">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="8">
+        <v>30</v>
+      </c>
+      <c r="H19" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1">
+      <c r="A20" s="87"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="8">
+        <v>20</v>
+      </c>
+      <c r="H20" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="14"/>
+      <c r="K20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" s="24"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="87"/>
+      <c r="B21" s="80" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="8">
+        <v>2</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" s="8">
+        <v>150</v>
+      </c>
+      <c r="H21" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" s="24"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="87"/>
+      <c r="B22" s="101" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="100" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="100">
+        <v>17</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="H22" s="13">
+        <v>3.4</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="14"/>
+      <c r="K22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" s="24"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="87"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
+      <c r="E23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="H23" s="13">
+        <v>-3.4</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23" s="14"/>
+      <c r="K23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" s="24"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="87"/>
+      <c r="B24" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="8">
+        <v>2</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G24" s="8">
+        <v>200</v>
+      </c>
+      <c r="H24" s="8">
+        <v>5</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="J24" s="14"/>
+      <c r="K24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" s="24"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="87"/>
+      <c r="B25" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="100">
+        <v>1</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="8">
+        <v>300</v>
+      </c>
+      <c r="H25" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" s="24"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="87"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="100"/>
+      <c r="E26" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="8">
+        <v>100</v>
+      </c>
+      <c r="H26" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="14"/>
+      <c r="K26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="M26" s="24"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="87"/>
+      <c r="B27" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G27" s="100">
+        <v>230</v>
+      </c>
+      <c r="H27" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="14"/>
+      <c r="K27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" s="24"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="87"/>
+      <c r="B28" s="80"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="G28" s="100"/>
+      <c r="H28" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" s="14"/>
+      <c r="K28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28" s="24"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="87"/>
+      <c r="B29" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="100" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="100">
+        <v>4</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="8">
+        <v>60</v>
+      </c>
+      <c r="H29" s="8">
+        <v>-5</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="J29" s="14"/>
+      <c r="K29" s="100" t="s">
+        <v>16</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="M29" s="31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="30">
+      <c r="A30" s="87"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="63">
+        <v>700</v>
+      </c>
+      <c r="H30" s="63">
+        <v>3.3</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="J30" s="75" t="s">
+        <v>194</v>
+      </c>
+      <c r="K30" s="100"/>
+      <c r="L30" s="89" t="s">
+        <v>186</v>
+      </c>
+      <c r="M30" s="90"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="87"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M31" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="87"/>
+      <c r="B32" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="100">
+        <v>16</v>
+      </c>
+      <c r="E32" s="91"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="87"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="100"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="100"/>
+      <c r="L33" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M33" s="24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="87"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M34" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="87"/>
+      <c r="B35" s="101"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G35" s="8">
+        <v>80</v>
+      </c>
+      <c r="H35" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="100"/>
+      <c r="L35" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35" s="24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="87"/>
+      <c r="B36" s="101"/>
+      <c r="C36" s="100"/>
+      <c r="D36" s="100"/>
+      <c r="E36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M36" s="24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="87"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="H37" s="8">
+        <v>-3.3</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="K37" s="100"/>
+      <c r="L37" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M37" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="87"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="100"/>
+      <c r="D38" s="100"/>
+      <c r="E38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="8">
+        <v>1.4E-2</v>
+      </c>
+      <c r="H38" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="J38" s="14"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M38" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="87"/>
+      <c r="B39" s="101"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="100"/>
+      <c r="E39" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="100"/>
+      <c r="L39" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39" s="24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="87"/>
+      <c r="B40" s="101"/>
+      <c r="C40" s="100"/>
+      <c r="D40" s="100"/>
+      <c r="E40" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" s="8">
+        <v>250</v>
+      </c>
+      <c r="H40" s="8">
+        <v>5</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="J40" s="14"/>
+      <c r="K40" s="100"/>
+      <c r="L40" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M40" s="24"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="87"/>
+      <c r="B41" s="101"/>
+      <c r="C41" s="100"/>
+      <c r="D41" s="100"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="M41" s="31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="87"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="100"/>
+      <c r="D42" s="100"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="100"/>
+      <c r="L42" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M42" s="24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="87"/>
+      <c r="B43" s="101"/>
+      <c r="C43" s="100"/>
+      <c r="D43" s="100"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="69"/>
+      <c r="K43" s="100"/>
+      <c r="L43" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M43" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="87"/>
+      <c r="B44" s="101"/>
+      <c r="C44" s="100"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M44" s="24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="87"/>
+      <c r="B45" s="101"/>
+      <c r="C45" s="100"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="104"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M45" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="87"/>
+      <c r="B46" s="101"/>
+      <c r="C46" s="100"/>
+      <c r="D46" s="100"/>
+      <c r="K46" s="100"/>
+      <c r="L46" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M46" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="87"/>
+      <c r="B47" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="8">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G47" s="8">
+        <v>10</v>
+      </c>
+      <c r="H47" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="14"/>
+      <c r="K47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M47" s="24"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="87"/>
+      <c r="B48" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="C48" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="D48" s="76">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" s="76">
+        <v>3.3</v>
+      </c>
+      <c r="G48" s="76">
+        <v>1</v>
+      </c>
+      <c r="H48" s="76">
+        <v>3.3</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="14"/>
+      <c r="K48" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" s="76"/>
+      <c r="M48" s="24"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="87"/>
+      <c r="B49" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" s="8">
+        <v>1</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G49" s="8">
+        <v>50</v>
+      </c>
+      <c r="H49" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" s="14"/>
+      <c r="K49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M49" s="24"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="87"/>
+      <c r="B50" s="80" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" s="8">
+        <v>1</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="8">
+        <v>1</v>
+      </c>
+      <c r="H50" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M50" s="24"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="87"/>
+      <c r="B51" s="80" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="8">
+        <v>2</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" s="8">
+        <v>1</v>
+      </c>
+      <c r="H51" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M51" s="24"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="87"/>
+      <c r="B52" s="101" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="100" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="100">
+        <v>2</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G52" s="8">
+        <v>50</v>
+      </c>
+      <c r="H52" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J52" s="14"/>
+      <c r="K52" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L52" s="8"/>
+      <c r="M52" s="24"/>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="87"/>
+      <c r="B53" s="101"/>
+      <c r="C53" s="100"/>
+      <c r="D53" s="100"/>
+      <c r="E53" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G53" s="8">
+        <v>50</v>
+      </c>
+      <c r="H53" s="8">
+        <v>-5.5</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="J53" s="14"/>
+      <c r="K53" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L53" s="8"/>
+      <c r="M53" s="24"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="87"/>
+      <c r="B54" s="101" t="s">
+        <v>187</v>
+      </c>
+      <c r="C54" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="100">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="8">
+        <v>2</v>
+      </c>
+      <c r="H54" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M54" s="24"/>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="87"/>
+      <c r="B55" s="101"/>
+      <c r="C55" s="100"/>
+      <c r="D55" s="100"/>
+      <c r="E55" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G55" s="8">
+        <v>1</v>
+      </c>
+      <c r="H55" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="14"/>
+      <c r="K55" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="M55" s="24"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A56" s="88"/>
+      <c r="B56" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D56" s="26">
+        <v>16</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="G56" s="26">
+        <v>6</v>
+      </c>
+      <c r="H56" s="26">
+        <v>3.3</v>
+      </c>
+      <c r="I56" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="J56" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="K56" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M56" s="27"/>
+    </row>
+    <row r="57" spans="1:13" ht="48.75" customHeight="1">
+      <c r="A57" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="B57" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="102" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" s="102">
+        <v>16</v>
+      </c>
+      <c r="E57" s="51"/>
+      <c r="F57" s="52"/>
+      <c r="G57" s="52"/>
+      <c r="H57" s="52"/>
+      <c r="I57" s="52"/>
+      <c r="J57" s="52"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="M57" s="34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="84"/>
+      <c r="B58" s="100"/>
+      <c r="C58" s="100"/>
+      <c r="D58" s="100"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
+      <c r="J58" s="67"/>
+      <c r="K58" s="56"/>
+      <c r="L58" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="M58" s="35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="84"/>
+      <c r="B59" s="100"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="100"/>
+      <c r="E59" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G59" s="18">
+        <v>2000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>22</v>
+      </c>
+      <c r="I59" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="J59" s="49"/>
+      <c r="K59" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="M59" s="36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="84"/>
+      <c r="B60" s="100"/>
+      <c r="C60" s="100"/>
+      <c r="D60" s="100"/>
+      <c r="E60" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G60" s="8">
         <v>10</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="5"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" s="14"/>
+      <c r="K60" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="M60" s="36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="84"/>
+      <c r="B61" s="100"/>
+      <c r="C61" s="100"/>
+      <c r="D61" s="100"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="58"/>
+      <c r="I61" s="58"/>
+      <c r="J61" s="64"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="M61" s="36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A62" s="85"/>
+      <c r="B62" s="103"/>
+      <c r="C62" s="103"/>
+      <c r="D62" s="103"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="61"/>
+      <c r="J62" s="61"/>
+      <c r="K62" s="62"/>
+      <c r="L62" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="M62" s="38" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="81" t="s">
+        <v>174</v>
+      </c>
+      <c r="B63" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="28">
+        <v>1</v>
+      </c>
+      <c r="E63" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G63" s="28">
+        <v>4000</v>
+      </c>
+      <c r="H63" s="28">
+        <v>20</v>
+      </c>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L63" s="28"/>
+      <c r="M63" s="30"/>
+    </row>
+    <row r="64" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A64" s="82"/>
+      <c r="B64" s="79" t="s">
+        <v>173</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26">
+        <v>1</v>
+      </c>
+      <c r="E64" s="25"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="47"/>
+      <c r="J64" s="47"/>
+      <c r="K64" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L64" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="M64" s="27"/>
+    </row>
+    <row r="69" spans="1:2" ht="18">
+      <c r="A69" s="43"/>
+      <c r="B69" s="41"/>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="B70" s="42"/>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="B72" s="42"/>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="B73" s="42"/>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="B74" s="44"/>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="B75" s="44"/>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="B76" s="44"/>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="B77" s="44"/>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="B78" s="42"/>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="B79" s="43"/>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="B80" s="42"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="42"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="44"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="44"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="44"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="44"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="42"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="43"/>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="42"/>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="42"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="44"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="44"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="44"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="44"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="42"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="43"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="42"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="42"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="44"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="M2:N2"/>
+  <mergeCells count="47">
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="D14:D18"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B32:B46"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="E41:I45"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A57:A62"/>
+    <mergeCell ref="A13:A56"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="E32:I34"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="D32:D46"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="C57:C62"/>
+    <mergeCell ref="D57:D62"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="K29:K46"/>
+    <mergeCell ref="C32:C46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>